--- a/data-request/dreq_AFR.xlsx
+++ b/data-request/dreq_AFR.xlsx
@@ -462,1000 +462,1000 @@
     <t>va200</t>
   </si>
   <si>
+    <t>va250</t>
+  </si>
+  <si>
+    <t>va300</t>
+  </si>
+  <si>
+    <t>va400</t>
+  </si>
+  <si>
+    <t>va500</t>
+  </si>
+  <si>
+    <t>va50m</t>
+  </si>
+  <si>
+    <t>va600</t>
+  </si>
+  <si>
+    <t>va700</t>
+  </si>
+  <si>
+    <t>va850</t>
+  </si>
+  <si>
+    <t>va925</t>
+  </si>
+  <si>
+    <t>wa1000</t>
+  </si>
+  <si>
+    <t>wa200</t>
+  </si>
+  <si>
+    <t>wa250</t>
+  </si>
+  <si>
+    <t>wa300</t>
+  </si>
+  <si>
+    <t>wa400</t>
+  </si>
+  <si>
+    <t>wa500</t>
+  </si>
+  <si>
+    <t>wa600</t>
+  </si>
+  <si>
+    <t>wa700</t>
+  </si>
+  <si>
+    <t>wa850</t>
+  </si>
+  <si>
+    <t>wa925</t>
+  </si>
+  <si>
+    <t>zg1000</t>
+  </si>
+  <si>
+    <t>zg200</t>
+  </si>
+  <si>
+    <t>zg250</t>
+  </si>
+  <si>
+    <t>zg300</t>
+  </si>
+  <si>
+    <t>zg400</t>
+  </si>
+  <si>
+    <t>zg500</t>
+  </si>
+  <si>
+    <t>zg600</t>
+  </si>
+  <si>
+    <t>zg700</t>
+  </si>
+  <si>
+    <t>zg850</t>
+  </si>
+  <si>
+    <t>zg925</t>
+  </si>
+  <si>
+    <t>zmla</t>
+  </si>
+  <si>
+    <t>atmosphere_mass_content_of_cloud_ice</t>
+  </si>
+  <si>
+    <t>atmosphere_mass_content_of_cloud_condensed_water</t>
+  </si>
+  <si>
+    <t>surface_upward_latent_heat_flux</t>
+  </si>
+  <si>
+    <t>surface_upward_sensible_heat_flux</t>
+  </si>
+  <si>
+    <t>soil_frozen_water_content</t>
+  </si>
+  <si>
+    <t>frozen_water_content_of_soil_layer</t>
+  </si>
+  <si>
+    <t>runoff_flux</t>
+  </si>
+  <si>
+    <t>surface_runoff_flux</t>
+  </si>
+  <si>
+    <t>mass_content_of_water_in_soil</t>
+  </si>
+  <si>
+    <t>mass_content_of_water_in_soil_layer</t>
+  </si>
+  <si>
+    <t>convective_precipitation_flux</t>
+  </si>
+  <si>
+    <t>snowfall_flux</t>
+  </si>
+  <si>
+    <t>atmosphere_mass_content_of_water_vapor</t>
+  </si>
+  <si>
+    <t>surface_upwelling_longwave_flux_in_air</t>
+  </si>
+  <si>
+    <t>toa_outgoing_longwave_flux</t>
+  </si>
+  <si>
+    <t>surface_direct_downwelling_shortwave_flux_in_air</t>
+  </si>
+  <si>
+    <t>toa_incoming_shortwave_flux</t>
+  </si>
+  <si>
+    <t>surface_upwelling_shortwave_flux_in_air</t>
+  </si>
+  <si>
+    <t>toa_outgoing_shortwave_flux</t>
+  </si>
+  <si>
+    <t>sea_ice_area_fraction</t>
+  </si>
+  <si>
+    <t>surface_snow_area_fraction</t>
+  </si>
+  <si>
+    <t>surface_snow_thickness</t>
+  </si>
+  <si>
+    <t>surface_snow_melt_flux</t>
+  </si>
+  <si>
+    <t>surface_snow_amount</t>
+  </si>
+  <si>
+    <t>duration_of_sunshine</t>
+  </si>
+  <si>
+    <t>surface_downward_eastward_stress</t>
+  </si>
+  <si>
+    <t>surface_downward_northward_stress</t>
+  </si>
+  <si>
+    <t>surface_temperature</t>
+  </si>
+  <si>
+    <t>soil_temperature</t>
+  </si>
+  <si>
+    <t>upward_air_velocity</t>
+  </si>
+  <si>
+    <t>geopotential_height</t>
+  </si>
+  <si>
+    <t>atmosphere_boundary_layer_thickness</t>
+  </si>
+  <si>
+    <t>Ice Water Path</t>
+  </si>
+  <si>
+    <t>Condensed Water Path</t>
+  </si>
+  <si>
+    <t>Surface Upward Latent Heat Flux</t>
+  </si>
+  <si>
+    <t>Surface Upward Sensible Heat Flux</t>
+  </si>
+  <si>
+    <t>Specific Humidity at 1000hPa</t>
+  </si>
+  <si>
+    <t>Specific Humidity at 200hPa</t>
+  </si>
+  <si>
+    <t>Specific Humidity at 250hPa</t>
+  </si>
+  <si>
+    <t>Specific Humidity at 300hPa</t>
+  </si>
+  <si>
+    <t>Specific Humidity at 400hPa</t>
+  </si>
+  <si>
+    <t>Specific Humidity at 500hPa</t>
+  </si>
+  <si>
+    <t>Specific Humidity at 50m</t>
+  </si>
+  <si>
+    <t>Specific Humidity at 600hPa</t>
+  </si>
+  <si>
+    <t>Specific Humidity at 700hPa</t>
+  </si>
+  <si>
+    <t>Specific Humidity at 850hPa</t>
+  </si>
+  <si>
+    <t>Specific Humidity at 925hPa</t>
+  </si>
+  <si>
+    <t>Soil Frozen Water Content</t>
+  </si>
+  <si>
+    <t>Frozen Water Content in Upper Portion of Soil Column</t>
+  </si>
+  <si>
+    <t>Total Runoff</t>
+  </si>
+  <si>
+    <t>Surface Runoff</t>
+  </si>
+  <si>
+    <t>Frozen Water Content of Soil Layer</t>
+  </si>
+  <si>
+    <t>Total Soil Moisture Content</t>
+  </si>
+  <si>
+    <t>Total Water Content of Soil Layer</t>
+  </si>
+  <si>
+    <t>Moisture in Upper Portion of Soil Column</t>
+  </si>
+  <si>
+    <t>Convective Precipitation</t>
+  </si>
+  <si>
+    <t>Daily Maximum Hourly Precipitation Rate</t>
+  </si>
+  <si>
+    <t>Snowfall Flux</t>
+  </si>
+  <si>
+    <t>Water Vapor Path</t>
+  </si>
+  <si>
+    <t>Surface Upwelling Longwave Radiation</t>
+  </si>
+  <si>
+    <t>TOA Outgoing Longwave Radiation</t>
+  </si>
+  <si>
+    <t>Surface Direct Downwelling Shortwave Radiation</t>
+  </si>
+  <si>
+    <t>TOA Incident Shortwave Radiation</t>
+  </si>
+  <si>
+    <t>Surface Upwelling Shortwave Radiation</t>
+  </si>
+  <si>
+    <t>TOA Outgoing Shortwave Radiation</t>
+  </si>
+  <si>
+    <t>Daily Maximum Near-Surface Wind Speed</t>
+  </si>
+  <si>
+    <t>Sea-Ice Area Percentage (Atmospheric Grid)</t>
+  </si>
+  <si>
+    <t>Snow Area Percentage</t>
+  </si>
+  <si>
+    <t>Snow Depth</t>
+  </si>
+  <si>
+    <t>Surface Snow Melt</t>
+  </si>
+  <si>
+    <t>Surface Snow Amount</t>
+  </si>
+  <si>
+    <t>Daily Duration of Sunshine</t>
+  </si>
+  <si>
+    <t>Air Temperature at 1000hPa</t>
+  </si>
+  <si>
+    <t>Air Temperature at 200hPa</t>
+  </si>
+  <si>
+    <t>Air Temperature at 250hPa</t>
+  </si>
+  <si>
+    <t>Air Temperature at 300hPa</t>
+  </si>
+  <si>
+    <t>Air Temperature at 400hPa</t>
+  </si>
+  <si>
+    <t>Air Temperature at 500hPa</t>
+  </si>
+  <si>
+    <t>Air Temperature at 50m</t>
+  </si>
+  <si>
+    <t>Air Temperature at 600hPa</t>
+  </si>
+  <si>
+    <t>Air Temperature at 700hPa</t>
+  </si>
+  <si>
+    <t>Air Temperature at 850hPa</t>
+  </si>
+  <si>
+    <t>Air Temperature at 925hPa</t>
+  </si>
+  <si>
+    <t>Surface Downward Eastward Wind Stress</t>
+  </si>
+  <si>
+    <t>Surface Downward Northward Wind Stress</t>
+  </si>
+  <si>
+    <t>Surface Temperature</t>
+  </si>
+  <si>
+    <t>Temperature of Soil</t>
+  </si>
+  <si>
+    <t>Eastward Wind at 1000hPa</t>
+  </si>
+  <si>
+    <t>Eastward Wind at 100m</t>
+  </si>
+  <si>
+    <t>Eastward Wind at 150m</t>
+  </si>
+  <si>
+    <t>Eastward Wind at 200hPa</t>
+  </si>
+  <si>
+    <t>Eastward Wind at 250hPa</t>
+  </si>
+  <si>
+    <t>Eastward Wind at 300hPa</t>
+  </si>
+  <si>
+    <t>Eastward Wind at 400hPa</t>
+  </si>
+  <si>
+    <t>Eastward Wind at 500hPa</t>
+  </si>
+  <si>
+    <t>Eastward Wind at 50m</t>
+  </si>
+  <si>
+    <t>Eastward Wind at 600hPa</t>
+  </si>
+  <si>
+    <t>Eastward Wind at 700hPa</t>
+  </si>
+  <si>
+    <t>Eastward Wind at 850hPa</t>
+  </si>
+  <si>
+    <t>Eastward Wind at 925hPa</t>
+  </si>
+  <si>
+    <t>Northward Wind at 1000hPa</t>
+  </si>
+  <si>
+    <t>Northward Wind at 100m</t>
+  </si>
+  <si>
+    <t>Northward Wind at 150m</t>
+  </si>
+  <si>
+    <t>Northward Wind at 200hPa</t>
+  </si>
+  <si>
+    <t>Northward Wind at 250hPa</t>
+  </si>
+  <si>
+    <t>Northward Wind at 300hPa</t>
+  </si>
+  <si>
+    <t>Northward Wind at 400hPa</t>
+  </si>
+  <si>
+    <t>Northward Wind at 500hPa</t>
+  </si>
+  <si>
+    <t>Northward Wind at 50m</t>
+  </si>
+  <si>
+    <t>Northward Wind at 600hPa</t>
+  </si>
+  <si>
+    <t>Northward Wind at 700hPa</t>
+  </si>
+  <si>
+    <t>Northward Wind at 850hPa</t>
+  </si>
+  <si>
+    <t>Northward Wind at 925hPa</t>
+  </si>
+  <si>
+    <t>Upward Air Velocity at 1000hPa</t>
+  </si>
+  <si>
+    <t>Upward Air Velocity at 200hPa</t>
+  </si>
+  <si>
+    <t>Upward Air Velocity at 250hPa</t>
+  </si>
+  <si>
+    <t>Upward Air Velocity at 300hPa</t>
+  </si>
+  <si>
+    <t>Upward Air Velocity at 400hPa</t>
+  </si>
+  <si>
+    <t>Upward Air Velocity at 500hPa</t>
+  </si>
+  <si>
+    <t>Upward Air Velocity at 600hPa</t>
+  </si>
+  <si>
+    <t>Upward Air Velocity at 700hPa</t>
+  </si>
+  <si>
+    <t>Upward Air Velocity at 850hPa</t>
+  </si>
+  <si>
+    <t>Upward Air Velocity at 925hPa</t>
+  </si>
+  <si>
+    <t>Geopotential Height at 1000hPa</t>
+  </si>
+  <si>
+    <t>Geopotential Height at 200hPa</t>
+  </si>
+  <si>
+    <t>Geopotential Height at 250hPa</t>
+  </si>
+  <si>
+    <t>Geopotential Height at 300hPa</t>
+  </si>
+  <si>
+    <t>Geopotential Height at 400hPa</t>
+  </si>
+  <si>
+    <t>Geopotential Height at 500hPa</t>
+  </si>
+  <si>
+    <t>Geopotential Height at 600hPa</t>
+  </si>
+  <si>
+    <t>Geopotential Height at 700hPa</t>
+  </si>
+  <si>
+    <t>Geopotential Height at 850hPa</t>
+  </si>
+  <si>
+    <t>Geopotential Height at 925hPa</t>
+  </si>
+  <si>
+    <t>Height of Boundary Layer</t>
+  </si>
+  <si>
+    <t>kg m-2</t>
+  </si>
+  <si>
+    <t>s</t>
+  </si>
+  <si>
+    <t>area: mean where land time: mean</t>
+  </si>
+  <si>
+    <t>area: mean where land time: point</t>
+  </si>
+  <si>
+    <t>area: mean time: mean within hours time: maximum over hours</t>
+  </si>
+  <si>
+    <t>time: sum</t>
+  </si>
+  <si>
+    <t>time: sum within days time: mean over days</t>
+  </si>
+  <si>
+    <t>['6hr']</t>
+  </si>
+  <si>
+    <t>['mon', 'day', '6hr']</t>
+  </si>
+  <si>
+    <t>areacella</t>
+  </si>
+  <si>
+    <t>cape</t>
+  </si>
+  <si>
+    <t>capemax</t>
+  </si>
+  <si>
+    <t>cin</t>
+  </si>
+  <si>
+    <t>cinmax</t>
+  </si>
+  <si>
+    <t>clh</t>
+  </si>
+  <si>
+    <t>cll</t>
+  </si>
+  <si>
+    <t>clm</t>
+  </si>
+  <si>
+    <t>dtb</t>
+  </si>
+  <si>
+    <t>evspsblpot</t>
+  </si>
+  <si>
+    <t>hus10</t>
+  </si>
+  <si>
+    <t>hus100</t>
+  </si>
+  <si>
+    <t>hus150</t>
+  </si>
+  <si>
+    <t>hus20</t>
+  </si>
+  <si>
+    <t>hus30</t>
+  </si>
+  <si>
+    <t>hus50</t>
+  </si>
+  <si>
+    <t>hus70</t>
+  </si>
+  <si>
+    <t>hus750</t>
+  </si>
+  <si>
+    <t>li</t>
+  </si>
+  <si>
+    <t>limax</t>
+  </si>
+  <si>
+    <t>mrsofc</t>
+  </si>
+  <si>
+    <t>od550aer</t>
+  </si>
+  <si>
+    <t>rldscs</t>
+  </si>
+  <si>
+    <t>rluscs</t>
+  </si>
+  <si>
+    <t>rlutcs</t>
+  </si>
+  <si>
+    <t>rootd</t>
+  </si>
+  <si>
+    <t>rsdscs</t>
+  </si>
+  <si>
+    <t>rsuscs</t>
+  </si>
+  <si>
+    <t>rsutcs</t>
+  </si>
+  <si>
+    <t>sftgif</t>
+  </si>
+  <si>
+    <t>sftlaf</t>
+  </si>
+  <si>
+    <t>sfturf</t>
+  </si>
+  <si>
+    <t>ta10</t>
+  </si>
+  <si>
+    <t>ta100</t>
+  </si>
+  <si>
+    <t>ta150</t>
+  </si>
+  <si>
+    <t>ta20</t>
+  </si>
+  <si>
+    <t>ta30</t>
+  </si>
+  <si>
+    <t>ta50</t>
+  </si>
+  <si>
+    <t>ta70</t>
+  </si>
+  <si>
+    <t>ta750</t>
+  </si>
+  <si>
+    <t>ua10</t>
+  </si>
+  <si>
+    <t>ua100</t>
+  </si>
+  <si>
+    <t>ua150</t>
+  </si>
+  <si>
+    <t>ua20</t>
+  </si>
+  <si>
+    <t>ua200m</t>
+  </si>
+  <si>
+    <t>ua250m</t>
+  </si>
+  <si>
+    <t>ua30</t>
+  </si>
+  <si>
+    <t>ua300m</t>
+  </si>
+  <si>
+    <t>ua50</t>
+  </si>
+  <si>
+    <t>ua70</t>
+  </si>
+  <si>
+    <t>ua750</t>
+  </si>
+  <si>
+    <t>va10</t>
+  </si>
+  <si>
+    <t>va100</t>
+  </si>
+  <si>
+    <t>va150</t>
+  </si>
+  <si>
+    <t>va20</t>
+  </si>
+  <si>
     <t>va200m</t>
   </si>
   <si>
-    <t>va250</t>
-  </si>
-  <si>
     <t>va250m</t>
   </si>
   <si>
-    <t>va300</t>
+    <t>va30</t>
   </si>
   <si>
     <t>va300m</t>
   </si>
   <si>
-    <t>va400</t>
-  </si>
-  <si>
-    <t>va500</t>
-  </si>
-  <si>
-    <t>va50m</t>
-  </si>
-  <si>
-    <t>va600</t>
-  </si>
-  <si>
-    <t>va700</t>
-  </si>
-  <si>
-    <t>va850</t>
-  </si>
-  <si>
-    <t>va925</t>
-  </si>
-  <si>
-    <t>wa1000</t>
-  </si>
-  <si>
-    <t>wa200</t>
-  </si>
-  <si>
-    <t>wa250</t>
-  </si>
-  <si>
-    <t>wa300</t>
-  </si>
-  <si>
-    <t>wa400</t>
-  </si>
-  <si>
-    <t>wa500</t>
-  </si>
-  <si>
-    <t>wa600</t>
-  </si>
-  <si>
-    <t>wa700</t>
-  </si>
-  <si>
-    <t>wa850</t>
-  </si>
-  <si>
-    <t>wa925</t>
-  </si>
-  <si>
-    <t>zg1000</t>
-  </si>
-  <si>
-    <t>zg200</t>
-  </si>
-  <si>
-    <t>zg250</t>
-  </si>
-  <si>
-    <t>zg300</t>
-  </si>
-  <si>
-    <t>zg400</t>
-  </si>
-  <si>
-    <t>zg500</t>
-  </si>
-  <si>
-    <t>zg600</t>
-  </si>
-  <si>
-    <t>zg700</t>
-  </si>
-  <si>
-    <t>zg850</t>
-  </si>
-  <si>
-    <t>zg925</t>
-  </si>
-  <si>
-    <t>zmla</t>
-  </si>
-  <si>
-    <t>atmosphere_mass_content_of_cloud_ice</t>
-  </si>
-  <si>
-    <t>atmosphere_mass_content_of_cloud_condensed_water</t>
-  </si>
-  <si>
-    <t>surface_upward_latent_heat_flux</t>
-  </si>
-  <si>
-    <t>surface_upward_sensible_heat_flux</t>
-  </si>
-  <si>
-    <t>soil_frozen_water_content</t>
-  </si>
-  <si>
-    <t>frozen_water_content_of_soil_layer</t>
-  </si>
-  <si>
-    <t>runoff_flux</t>
-  </si>
-  <si>
-    <t>surface_runoff_flux</t>
-  </si>
-  <si>
-    <t>mass_content_of_water_in_soil</t>
-  </si>
-  <si>
-    <t>mass_content_of_water_in_soil_layer</t>
-  </si>
-  <si>
-    <t>convective_precipitation_flux</t>
-  </si>
-  <si>
-    <t>snowfall_flux</t>
-  </si>
-  <si>
-    <t>atmosphere_mass_content_of_water_vapor</t>
-  </si>
-  <si>
-    <t>surface_upwelling_longwave_flux_in_air</t>
-  </si>
-  <si>
-    <t>toa_outgoing_longwave_flux</t>
-  </si>
-  <si>
-    <t>surface_direct_downwelling_shortwave_flux_in_air</t>
-  </si>
-  <si>
-    <t>toa_incoming_shortwave_flux</t>
-  </si>
-  <si>
-    <t>surface_upwelling_shortwave_flux_in_air</t>
-  </si>
-  <si>
-    <t>toa_outgoing_shortwave_flux</t>
-  </si>
-  <si>
-    <t>sea_ice_area_fraction</t>
-  </si>
-  <si>
-    <t>surface_snow_area_fraction</t>
-  </si>
-  <si>
-    <t>surface_snow_thickness</t>
-  </si>
-  <si>
-    <t>surface_snow_melt_flux</t>
-  </si>
-  <si>
-    <t>surface_snow_amount</t>
-  </si>
-  <si>
-    <t>duration_of_sunshine</t>
-  </si>
-  <si>
-    <t>surface_downward_eastward_stress</t>
-  </si>
-  <si>
-    <t>surface_downward_northward_stress</t>
-  </si>
-  <si>
-    <t>surface_temperature</t>
-  </si>
-  <si>
-    <t>soil_temperature</t>
-  </si>
-  <si>
-    <t>upward_air_velocity</t>
-  </si>
-  <si>
-    <t>geopotential_height</t>
-  </si>
-  <si>
-    <t>atmosphere_boundary_layer_thickness</t>
-  </si>
-  <si>
-    <t>Ice Water Path</t>
-  </si>
-  <si>
-    <t>Condensed Water Path</t>
-  </si>
-  <si>
-    <t>Surface Upward Latent Heat Flux</t>
-  </si>
-  <si>
-    <t>Surface Upward Sensible Heat Flux</t>
-  </si>
-  <si>
-    <t>Specific Humidity at 1000hPa</t>
-  </si>
-  <si>
-    <t>Specific Humidity at 200hPa</t>
-  </si>
-  <si>
-    <t>Specific Humidity at 250hPa</t>
-  </si>
-  <si>
-    <t>Specific Humidity at 300hPa</t>
-  </si>
-  <si>
-    <t>Specific Humidity at 400hPa</t>
-  </si>
-  <si>
-    <t>Specific Humidity at 500hPa</t>
-  </si>
-  <si>
-    <t>Specific Humidity at 50m</t>
-  </si>
-  <si>
-    <t>Specific Humidity at 600hPa</t>
-  </si>
-  <si>
-    <t>Specific Humidity at 700hPa</t>
-  </si>
-  <si>
-    <t>Specific Humidity at 850hPa</t>
-  </si>
-  <si>
-    <t>Specific Humidity at 925hPa</t>
-  </si>
-  <si>
-    <t>Soil Frozen Water Content</t>
-  </si>
-  <si>
-    <t>Frozen Water Content in Upper Portion of Soil Column</t>
-  </si>
-  <si>
-    <t>Total Runoff</t>
-  </si>
-  <si>
-    <t>Surface Runoff</t>
-  </si>
-  <si>
-    <t>Frozen Water Content of Soil Layer</t>
-  </si>
-  <si>
-    <t>Total Soil Moisture Content</t>
-  </si>
-  <si>
-    <t>Total Water Content of Soil Layer</t>
-  </si>
-  <si>
-    <t>Moisture in Upper Portion of Soil Column</t>
-  </si>
-  <si>
-    <t>Convective Precipitation</t>
-  </si>
-  <si>
-    <t>Daily Maximum Hourly Precipitation Rate</t>
-  </si>
-  <si>
-    <t>Snowfall Flux</t>
-  </si>
-  <si>
-    <t>Water Vapor Path</t>
-  </si>
-  <si>
-    <t>Surface Upwelling Longwave Radiation</t>
-  </si>
-  <si>
-    <t>TOA Outgoing Longwave Radiation</t>
-  </si>
-  <si>
-    <t>Surface Direct Downwelling Shortwave Radiation</t>
-  </si>
-  <si>
-    <t>TOA Incident Shortwave Radiation</t>
-  </si>
-  <si>
-    <t>Surface Upwelling Shortwave Radiation</t>
-  </si>
-  <si>
-    <t>TOA Outgoing Shortwave Radiation</t>
-  </si>
-  <si>
-    <t>Daily Maximum Near-Surface Wind Speed</t>
-  </si>
-  <si>
-    <t>Sea-Ice Area Percentage (Atmospheric Grid)</t>
-  </si>
-  <si>
-    <t>Snow Area Percentage</t>
-  </si>
-  <si>
-    <t>Snow Depth</t>
-  </si>
-  <si>
-    <t>Surface Snow Melt</t>
-  </si>
-  <si>
-    <t>Surface Snow Amount</t>
-  </si>
-  <si>
-    <t>Daily Duration of Sunshine</t>
-  </si>
-  <si>
-    <t>Air Temperature at 1000hPa</t>
-  </si>
-  <si>
-    <t>Air Temperature at 200hPa</t>
-  </si>
-  <si>
-    <t>Air Temperature at 250hPa</t>
-  </si>
-  <si>
-    <t>Air Temperature at 300hPa</t>
-  </si>
-  <si>
-    <t>Air Temperature at 400hPa</t>
-  </si>
-  <si>
-    <t>Air Temperature at 500hPa</t>
-  </si>
-  <si>
-    <t>Air Temperature at 50m</t>
-  </si>
-  <si>
-    <t>Air Temperature at 600hPa</t>
-  </si>
-  <si>
-    <t>Air Temperature at 700hPa</t>
-  </si>
-  <si>
-    <t>Air Temperature at 850hPa</t>
-  </si>
-  <si>
-    <t>Air Temperature at 925hPa</t>
-  </si>
-  <si>
-    <t>Surface Downward Eastward Wind Stress</t>
-  </si>
-  <si>
-    <t>Surface Downward Northward Wind Stress</t>
-  </si>
-  <si>
-    <t>Surface Temperature</t>
-  </si>
-  <si>
-    <t>Temperature of Soil</t>
-  </si>
-  <si>
-    <t>Eastward Wind at 1000hPa</t>
-  </si>
-  <si>
-    <t>Eastward Wind at 100m</t>
-  </si>
-  <si>
-    <t>Eastward Wind at 150m</t>
-  </si>
-  <si>
-    <t>Eastward Wind at 200hPa</t>
-  </si>
-  <si>
-    <t>Eastward Wind at 250hPa</t>
-  </si>
-  <si>
-    <t>Eastward Wind at 300hPa</t>
-  </si>
-  <si>
-    <t>Eastward Wind at 400hPa</t>
-  </si>
-  <si>
-    <t>Eastward Wind at 500hPa</t>
-  </si>
-  <si>
-    <t>Eastward Wind at 50m</t>
-  </si>
-  <si>
-    <t>Eastward Wind at 600hPa</t>
-  </si>
-  <si>
-    <t>Eastward Wind at 700hPa</t>
-  </si>
-  <si>
-    <t>Eastward Wind at 850hPa</t>
-  </si>
-  <si>
-    <t>Eastward Wind at 925hPa</t>
-  </si>
-  <si>
-    <t>Northward Wind at 1000hPa</t>
-  </si>
-  <si>
-    <t>Northward Wind at 100m</t>
-  </si>
-  <si>
-    <t>Northward Wind at 150m</t>
-  </si>
-  <si>
-    <t>Northward Wind at 200hPa</t>
+    <t>va50</t>
+  </si>
+  <si>
+    <t>va70</t>
+  </si>
+  <si>
+    <t>va750</t>
+  </si>
+  <si>
+    <t>wa10</t>
+  </si>
+  <si>
+    <t>wa100</t>
+  </si>
+  <si>
+    <t>wa150</t>
+  </si>
+  <si>
+    <t>wa20</t>
+  </si>
+  <si>
+    <t>wa30</t>
+  </si>
+  <si>
+    <t>wa50</t>
+  </si>
+  <si>
+    <t>wa70</t>
+  </si>
+  <si>
+    <t>wa750</t>
+  </si>
+  <si>
+    <t>wsgsmax</t>
+  </si>
+  <si>
+    <t>z0</t>
+  </si>
+  <si>
+    <t>zg10</t>
+  </si>
+  <si>
+    <t>zg100</t>
+  </si>
+  <si>
+    <t>zg150</t>
+  </si>
+  <si>
+    <t>zg20</t>
+  </si>
+  <si>
+    <t>zg30</t>
+  </si>
+  <si>
+    <t>zg50</t>
+  </si>
+  <si>
+    <t>zg70</t>
+  </si>
+  <si>
+    <t>zg750</t>
+  </si>
+  <si>
+    <t>cell_area</t>
+  </si>
+  <si>
+    <t>atmosphere_convective_available_potential_energy_wrt_surface</t>
+  </si>
+  <si>
+    <t>atmosphere_convective_inhibition_wrt_surface</t>
+  </si>
+  <si>
+    <t>cloud_area_fraction_in_atmosphere_layer</t>
+  </si>
+  <si>
+    <t>bedrock_depth_below_ground_level</t>
+  </si>
+  <si>
+    <t>water_potential_evaporation_flux</t>
+  </si>
+  <si>
+    <t>temperature_difference_between_ambient_air_and_air_lifted_adiabatically_from_the_surface</t>
+  </si>
+  <si>
+    <t>soil_moisture_content_at_field_capacity</t>
+  </si>
+  <si>
+    <t>atmosphere_optical_thickness_due_to_ambient_aerosol_particles</t>
+  </si>
+  <si>
+    <t>surface_downwelling_longwave_flux_in_air_assuming_clear_sky</t>
+  </si>
+  <si>
+    <t>surface_upwelling_longwave_flux_in_air_assuming_clear_sky</t>
+  </si>
+  <si>
+    <t>toa_outgoing_longwave_flux_assuming_clear_sky</t>
+  </si>
+  <si>
+    <t>root_depth</t>
+  </si>
+  <si>
+    <t>surface_downwelling_shortwave_flux_in_air_assuming_clear_sky</t>
+  </si>
+  <si>
+    <t>surface_upwelling_shortwave_flux_in_air_assuming_clear_sky</t>
+  </si>
+  <si>
+    <t>toa_outgoing_shortwave_flux_assuming_clear_sky</t>
+  </si>
+  <si>
+    <t>land_ice_area_fraction</t>
+  </si>
+  <si>
+    <t>area_fraction</t>
+  </si>
+  <si>
+    <t>wind_speed_of_gust</t>
+  </si>
+  <si>
+    <t>surface_roughness_length</t>
+  </si>
+  <si>
+    <t>Atmosphere Grid-Cell Area</t>
+  </si>
+  <si>
+    <t>Convective Available Potential Energy</t>
+  </si>
+  <si>
+    <t>Daily Maximum Convective Available Potential Energy</t>
+  </si>
+  <si>
+    <t>Convective Inhibition</t>
+  </si>
+  <si>
+    <t>Daily Maximum Convective Inhibition</t>
+  </si>
+  <si>
+    <t>High Level Cloud Fraction</t>
+  </si>
+  <si>
+    <t>Low Level Cloud Fraction</t>
+  </si>
+  <si>
+    <t>Mid Level Cloud Fraction</t>
+  </si>
+  <si>
+    <t>Depth to Bedrock</t>
+  </si>
+  <si>
+    <t>Potential Evapotranspiration</t>
+  </si>
+  <si>
+    <t>Specific Humidity at 10hPa</t>
+  </si>
+  <si>
+    <t>Specific Humidity at 100hPa</t>
+  </si>
+  <si>
+    <t>Specific Humidity at 150hPa</t>
+  </si>
+  <si>
+    <t>Specific Humidity at 20hPa</t>
+  </si>
+  <si>
+    <t>Specific Humidity at 30hPa</t>
+  </si>
+  <si>
+    <t>Specific Humidity at 50hPa</t>
+  </si>
+  <si>
+    <t>Specific Humidity at 70hPa</t>
+  </si>
+  <si>
+    <t>Specific Humidity at 750hPa</t>
+  </si>
+  <si>
+    <t>Lifted Index</t>
+  </si>
+  <si>
+    <t>Daily Maximum Lifted Index</t>
+  </si>
+  <si>
+    <t>Capacity of Soil to Store Water  (Field Capacity)</t>
+  </si>
+  <si>
+    <t>Ambient Aerosol Optical Thickness at 550nm</t>
+  </si>
+  <si>
+    <t>Surface Downwelling Clear-Sky Longwave Radiation</t>
+  </si>
+  <si>
+    <t>Surface Upwelling Clear-Sky Longwave Radiation</t>
+  </si>
+  <si>
+    <t>TOA Outgoing Clear-Sky Longwave Radiation</t>
+  </si>
+  <si>
+    <t>Maximum Root Depth</t>
+  </si>
+  <si>
+    <t>Surface Downwelling Clear-Sky Shortwave Radiation</t>
+  </si>
+  <si>
+    <t>Surface Upwelling Clear-Sky Shortwave Radiation</t>
+  </si>
+  <si>
+    <t>TOA Outgoing Clear-Sky Shortwave Radiation</t>
+  </si>
+  <si>
+    <t>Percentage of the Grid Cell Covered by Glacier</t>
+  </si>
+  <si>
+    <t>Percentage of the Grid Cell Occupied by Lake</t>
+  </si>
+  <si>
+    <t>Percentage of the Grid Cell Occupied by Urban Area</t>
+  </si>
+  <si>
+    <t>Air Temperature at 10hPa</t>
+  </si>
+  <si>
+    <t>Air Temperature at 100hPa</t>
+  </si>
+  <si>
+    <t>Air Temperature at 150hPa</t>
+  </si>
+  <si>
+    <t>Air Temperature at 20hPa</t>
+  </si>
+  <si>
+    <t>Air Temperature at 30hPa</t>
+  </si>
+  <si>
+    <t>Air Temperature at 50hPa</t>
+  </si>
+  <si>
+    <t>Air Temperature at 70hPa</t>
+  </si>
+  <si>
+    <t>Air Temperature at 750hPa</t>
+  </si>
+  <si>
+    <t>Eastward Wind at 10hPa</t>
+  </si>
+  <si>
+    <t>Eastward Wind at 100hPa</t>
+  </si>
+  <si>
+    <t>Eastward Wind at 150hPa</t>
+  </si>
+  <si>
+    <t>Eastward Wind at 20hPa</t>
+  </si>
+  <si>
+    <t>Eastward Wind at 200m</t>
+  </si>
+  <si>
+    <t>Eastward Wind at 250m</t>
+  </si>
+  <si>
+    <t>Eastward Wind at 30hPa</t>
+  </si>
+  <si>
+    <t>Eastward Wind at 300m</t>
+  </si>
+  <si>
+    <t>Eastward Wind at 50hPa</t>
+  </si>
+  <si>
+    <t>Eastward Wind at 70hPa</t>
+  </si>
+  <si>
+    <t>Eastward Wind at 750hPa</t>
+  </si>
+  <si>
+    <t>Northward Wind at 10hPa</t>
+  </si>
+  <si>
+    <t>Northward Wind at 100hPa</t>
+  </si>
+  <si>
+    <t>Northward Wind at 150hPa</t>
+  </si>
+  <si>
+    <t>Northward Wind at 20hPa</t>
   </si>
   <si>
     <t>Northward Wind at 200m</t>
   </si>
   <si>
-    <t>Northward Wind at 250hPa</t>
-  </si>
-  <si>
     <t>Northward Wind at 250m</t>
   </si>
   <si>
-    <t>Northward Wind at 300hPa</t>
+    <t>Northward Wind at 30hPa</t>
   </si>
   <si>
     <t>Northward Wind at 300m</t>
-  </si>
-  <si>
-    <t>Northward Wind at 400hPa</t>
-  </si>
-  <si>
-    <t>Northward Wind at 500hPa</t>
-  </si>
-  <si>
-    <t>Northward Wind at 50m</t>
-  </si>
-  <si>
-    <t>Northward Wind at 600hPa</t>
-  </si>
-  <si>
-    <t>Northward Wind at 700hPa</t>
-  </si>
-  <si>
-    <t>Northward Wind at 850hPa</t>
-  </si>
-  <si>
-    <t>Northward Wind at 925hPa</t>
-  </si>
-  <si>
-    <t>Upward Air Velocity at 1000hPa</t>
-  </si>
-  <si>
-    <t>Upward Air Velocity at 200hPa</t>
-  </si>
-  <si>
-    <t>Upward Air Velocity at 250hPa</t>
-  </si>
-  <si>
-    <t>Upward Air Velocity at 300hPa</t>
-  </si>
-  <si>
-    <t>Upward Air Velocity at 400hPa</t>
-  </si>
-  <si>
-    <t>Upward Air Velocity at 500hPa</t>
-  </si>
-  <si>
-    <t>Upward Air Velocity at 600hPa</t>
-  </si>
-  <si>
-    <t>Upward Air Velocity at 700hPa</t>
-  </si>
-  <si>
-    <t>Upward Air Velocity at 850hPa</t>
-  </si>
-  <si>
-    <t>Upward Air Velocity at 925hPa</t>
-  </si>
-  <si>
-    <t>Geopotential Height at 1000hPa</t>
-  </si>
-  <si>
-    <t>Geopotential Height at 200hPa</t>
-  </si>
-  <si>
-    <t>Geopotential Height at 250hPa</t>
-  </si>
-  <si>
-    <t>Geopotential Height at 300hPa</t>
-  </si>
-  <si>
-    <t>Geopotential Height at 400hPa</t>
-  </si>
-  <si>
-    <t>Geopotential Height at 500hPa</t>
-  </si>
-  <si>
-    <t>Geopotential Height at 600hPa</t>
-  </si>
-  <si>
-    <t>Geopotential Height at 700hPa</t>
-  </si>
-  <si>
-    <t>Geopotential Height at 850hPa</t>
-  </si>
-  <si>
-    <t>Geopotential Height at 925hPa</t>
-  </si>
-  <si>
-    <t>Height of Boundary Layer</t>
-  </si>
-  <si>
-    <t>kg m-2</t>
-  </si>
-  <si>
-    <t>s</t>
-  </si>
-  <si>
-    <t>area: mean where land time: mean</t>
-  </si>
-  <si>
-    <t>area: mean where land time: point</t>
-  </si>
-  <si>
-    <t>area: mean time: mean within hours time: maximum over hours</t>
-  </si>
-  <si>
-    <t>time: sum</t>
-  </si>
-  <si>
-    <t>time: sum within days time: mean over days</t>
-  </si>
-  <si>
-    <t>['6hr']</t>
-  </si>
-  <si>
-    <t>['mon', 'day', '6hr']</t>
-  </si>
-  <si>
-    <t>areacella</t>
-  </si>
-  <si>
-    <t>cape</t>
-  </si>
-  <si>
-    <t>capemax</t>
-  </si>
-  <si>
-    <t>cin</t>
-  </si>
-  <si>
-    <t>cinmax</t>
-  </si>
-  <si>
-    <t>clh</t>
-  </si>
-  <si>
-    <t>cll</t>
-  </si>
-  <si>
-    <t>clm</t>
-  </si>
-  <si>
-    <t>dtb</t>
-  </si>
-  <si>
-    <t>evspsblpot</t>
-  </si>
-  <si>
-    <t>hus10</t>
-  </si>
-  <si>
-    <t>hus100</t>
-  </si>
-  <si>
-    <t>hus150</t>
-  </si>
-  <si>
-    <t>hus20</t>
-  </si>
-  <si>
-    <t>hus30</t>
-  </si>
-  <si>
-    <t>hus50</t>
-  </si>
-  <si>
-    <t>hus70</t>
-  </si>
-  <si>
-    <t>hus750</t>
-  </si>
-  <si>
-    <t>li</t>
-  </si>
-  <si>
-    <t>limax</t>
-  </si>
-  <si>
-    <t>mrsofc</t>
-  </si>
-  <si>
-    <t>od550aer</t>
-  </si>
-  <si>
-    <t>rldscs</t>
-  </si>
-  <si>
-    <t>rluscs</t>
-  </si>
-  <si>
-    <t>rlutcs</t>
-  </si>
-  <si>
-    <t>rootd</t>
-  </si>
-  <si>
-    <t>rsdscs</t>
-  </si>
-  <si>
-    <t>rsuscs</t>
-  </si>
-  <si>
-    <t>rsutcs</t>
-  </si>
-  <si>
-    <t>sftgif</t>
-  </si>
-  <si>
-    <t>sftlaf</t>
-  </si>
-  <si>
-    <t>sfturf</t>
-  </si>
-  <si>
-    <t>ta10</t>
-  </si>
-  <si>
-    <t>ta100</t>
-  </si>
-  <si>
-    <t>ta150</t>
-  </si>
-  <si>
-    <t>ta20</t>
-  </si>
-  <si>
-    <t>ta30</t>
-  </si>
-  <si>
-    <t>ta50</t>
-  </si>
-  <si>
-    <t>ta70</t>
-  </si>
-  <si>
-    <t>ta750</t>
-  </si>
-  <si>
-    <t>ua10</t>
-  </si>
-  <si>
-    <t>ua100</t>
-  </si>
-  <si>
-    <t>ua150</t>
-  </si>
-  <si>
-    <t>ua20</t>
-  </si>
-  <si>
-    <t>ua200m</t>
-  </si>
-  <si>
-    <t>ua250m</t>
-  </si>
-  <si>
-    <t>ua30</t>
-  </si>
-  <si>
-    <t>ua300m</t>
-  </si>
-  <si>
-    <t>ua50</t>
-  </si>
-  <si>
-    <t>ua70</t>
-  </si>
-  <si>
-    <t>ua750</t>
-  </si>
-  <si>
-    <t>va10</t>
-  </si>
-  <si>
-    <t>va100</t>
-  </si>
-  <si>
-    <t>va150</t>
-  </si>
-  <si>
-    <t>va20</t>
-  </si>
-  <si>
-    <t>va30</t>
-  </si>
-  <si>
-    <t>va50</t>
-  </si>
-  <si>
-    <t>va70</t>
-  </si>
-  <si>
-    <t>va750</t>
-  </si>
-  <si>
-    <t>wa10</t>
-  </si>
-  <si>
-    <t>wa100</t>
-  </si>
-  <si>
-    <t>wa150</t>
-  </si>
-  <si>
-    <t>wa20</t>
-  </si>
-  <si>
-    <t>wa30</t>
-  </si>
-  <si>
-    <t>wa50</t>
-  </si>
-  <si>
-    <t>wa70</t>
-  </si>
-  <si>
-    <t>wa750</t>
-  </si>
-  <si>
-    <t>wsgsmax</t>
-  </si>
-  <si>
-    <t>z0</t>
-  </si>
-  <si>
-    <t>zg10</t>
-  </si>
-  <si>
-    <t>zg100</t>
-  </si>
-  <si>
-    <t>zg150</t>
-  </si>
-  <si>
-    <t>zg20</t>
-  </si>
-  <si>
-    <t>zg30</t>
-  </si>
-  <si>
-    <t>zg50</t>
-  </si>
-  <si>
-    <t>zg70</t>
-  </si>
-  <si>
-    <t>zg750</t>
-  </si>
-  <si>
-    <t>cell_area</t>
-  </si>
-  <si>
-    <t>atmosphere_convective_available_potential_energy_wrt_surface</t>
-  </si>
-  <si>
-    <t>atmosphere_convective_inhibition_wrt_surface</t>
-  </si>
-  <si>
-    <t>cloud_area_fraction_in_atmosphere_layer</t>
-  </si>
-  <si>
-    <t>bedrock_depth_below_ground_level</t>
-  </si>
-  <si>
-    <t>water_potential_evaporation_flux</t>
-  </si>
-  <si>
-    <t>temperature_difference_between_ambient_air_and_air_lifted_adiabatically_from_the_surface</t>
-  </si>
-  <si>
-    <t>soil_moisture_content_at_field_capacity</t>
-  </si>
-  <si>
-    <t>atmosphere_optical_thickness_due_to_ambient_aerosol_particles</t>
-  </si>
-  <si>
-    <t>surface_downwelling_longwave_flux_in_air_assuming_clear_sky</t>
-  </si>
-  <si>
-    <t>surface_upwelling_longwave_flux_in_air_assuming_clear_sky</t>
-  </si>
-  <si>
-    <t>toa_outgoing_longwave_flux_assuming_clear_sky</t>
-  </si>
-  <si>
-    <t>root_depth</t>
-  </si>
-  <si>
-    <t>surface_downwelling_shortwave_flux_in_air_assuming_clear_sky</t>
-  </si>
-  <si>
-    <t>surface_upwelling_shortwave_flux_in_air_assuming_clear_sky</t>
-  </si>
-  <si>
-    <t>toa_outgoing_shortwave_flux_assuming_clear_sky</t>
-  </si>
-  <si>
-    <t>land_ice_area_fraction</t>
-  </si>
-  <si>
-    <t>area_fraction</t>
-  </si>
-  <si>
-    <t>wind_speed_of_gust</t>
-  </si>
-  <si>
-    <t>surface_roughness_length</t>
-  </si>
-  <si>
-    <t>Atmosphere Grid-Cell Area</t>
-  </si>
-  <si>
-    <t>Convective Available Potential Energy</t>
-  </si>
-  <si>
-    <t>Daily Maximum Convective Available Potential Energy</t>
-  </si>
-  <si>
-    <t>Convective Inhibition</t>
-  </si>
-  <si>
-    <t>Daily Maximum Convective Inhibition</t>
-  </si>
-  <si>
-    <t>High Level Cloud Fraction</t>
-  </si>
-  <si>
-    <t>Low Level Cloud Fraction</t>
-  </si>
-  <si>
-    <t>Mid Level Cloud Fraction</t>
-  </si>
-  <si>
-    <t>Depth to Bedrock</t>
-  </si>
-  <si>
-    <t>Potential Evapotranspiration</t>
-  </si>
-  <si>
-    <t>Specific Humidity at 10hPa</t>
-  </si>
-  <si>
-    <t>Specific Humidity at 100hPa</t>
-  </si>
-  <si>
-    <t>Specific Humidity at 150hPa</t>
-  </si>
-  <si>
-    <t>Specific Humidity at 20hPa</t>
-  </si>
-  <si>
-    <t>Specific Humidity at 30hPa</t>
-  </si>
-  <si>
-    <t>Specific Humidity at 50hPa</t>
-  </si>
-  <si>
-    <t>Specific Humidity at 70hPa</t>
-  </si>
-  <si>
-    <t>Specific Humidity at 750hPa</t>
-  </si>
-  <si>
-    <t>Lifted Index</t>
-  </si>
-  <si>
-    <t>Daily Maximum Lifted Index</t>
-  </si>
-  <si>
-    <t>Capacity of Soil to Store Water  (Field Capacity)</t>
-  </si>
-  <si>
-    <t>Ambient Aerosol Optical Thickness at 550nm</t>
-  </si>
-  <si>
-    <t>Surface Downwelling Clear-Sky Longwave Radiation</t>
-  </si>
-  <si>
-    <t>Surface Upwelling Clear-Sky Longwave Radiation</t>
-  </si>
-  <si>
-    <t>TOA Outgoing Clear-Sky Longwave Radiation</t>
-  </si>
-  <si>
-    <t>Maximum Root Depth</t>
-  </si>
-  <si>
-    <t>Surface Downwelling Clear-Sky Shortwave Radiation</t>
-  </si>
-  <si>
-    <t>Surface Upwelling Clear-Sky Shortwave Radiation</t>
-  </si>
-  <si>
-    <t>TOA Outgoing Clear-Sky Shortwave Radiation</t>
-  </si>
-  <si>
-    <t>Percentage of the Grid Cell Covered by Glacier</t>
-  </si>
-  <si>
-    <t>Percentage of the Grid Cell Occupied by Lake</t>
-  </si>
-  <si>
-    <t>Percentage of the Grid Cell Occupied by Urban Area</t>
-  </si>
-  <si>
-    <t>Air Temperature at 10hPa</t>
-  </si>
-  <si>
-    <t>Air Temperature at 100hPa</t>
-  </si>
-  <si>
-    <t>Air Temperature at 150hPa</t>
-  </si>
-  <si>
-    <t>Air Temperature at 20hPa</t>
-  </si>
-  <si>
-    <t>Air Temperature at 30hPa</t>
-  </si>
-  <si>
-    <t>Air Temperature at 50hPa</t>
-  </si>
-  <si>
-    <t>Air Temperature at 70hPa</t>
-  </si>
-  <si>
-    <t>Air Temperature at 750hPa</t>
-  </si>
-  <si>
-    <t>Eastward Wind at 10hPa</t>
-  </si>
-  <si>
-    <t>Eastward Wind at 100hPa</t>
-  </si>
-  <si>
-    <t>Eastward Wind at 150hPa</t>
-  </si>
-  <si>
-    <t>Eastward Wind at 20hPa</t>
-  </si>
-  <si>
-    <t>Eastward Wind at 200m</t>
-  </si>
-  <si>
-    <t>Eastward Wind at 250m</t>
-  </si>
-  <si>
-    <t>Eastward Wind at 30hPa</t>
-  </si>
-  <si>
-    <t>Eastward Wind at 300m</t>
-  </si>
-  <si>
-    <t>Eastward Wind at 50hPa</t>
-  </si>
-  <si>
-    <t>Eastward Wind at 70hPa</t>
-  </si>
-  <si>
-    <t>Eastward Wind at 750hPa</t>
-  </si>
-  <si>
-    <t>Northward Wind at 10hPa</t>
-  </si>
-  <si>
-    <t>Northward Wind at 100hPa</t>
-  </si>
-  <si>
-    <t>Northward Wind at 150hPa</t>
-  </si>
-  <si>
-    <t>Northward Wind at 20hPa</t>
-  </si>
-  <si>
-    <t>Northward Wind at 30hPa</t>
   </si>
   <si>
     <t>Northward Wind at 50hPa</t>
@@ -2423,7 +2423,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F194"/>
+  <dimension ref="A1:F188"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="6" width="40.7109375" customWidth="1"/>
@@ -2454,13 +2454,13 @@
         <v>76</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>64</v>
@@ -2486,13 +2486,13 @@
         <v>77</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>64</v>
@@ -2518,10 +2518,10 @@
         <v>78</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>60</v>
@@ -2538,10 +2538,10 @@
         <v>79</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>60</v>
@@ -2561,7 +2561,7 @@
         <v>26</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>57</v>
@@ -2570,7 +2570,7 @@
         <v>64</v>
       </c>
       <c r="F8" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -2593,7 +2593,7 @@
         <v>26</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>57</v>
@@ -2602,7 +2602,7 @@
         <v>64</v>
       </c>
       <c r="F10" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -2625,7 +2625,7 @@
         <v>26</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>57</v>
@@ -2634,7 +2634,7 @@
         <v>64</v>
       </c>
       <c r="F12" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -2657,7 +2657,7 @@
         <v>26</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>57</v>
@@ -2666,7 +2666,7 @@
         <v>64</v>
       </c>
       <c r="F14" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -2689,7 +2689,7 @@
         <v>26</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>57</v>
@@ -2698,7 +2698,7 @@
         <v>64</v>
       </c>
       <c r="F16" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -2721,7 +2721,7 @@
         <v>26</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>57</v>
@@ -2730,7 +2730,7 @@
         <v>64</v>
       </c>
       <c r="F18" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -2753,7 +2753,7 @@
         <v>26</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>57</v>
@@ -2785,7 +2785,7 @@
         <v>26</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>57</v>
@@ -2794,7 +2794,7 @@
         <v>64</v>
       </c>
       <c r="F22" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -2817,7 +2817,7 @@
         <v>26</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>57</v>
@@ -2826,7 +2826,7 @@
         <v>64</v>
       </c>
       <c r="F24" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -2849,7 +2849,7 @@
         <v>26</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>57</v>
@@ -2858,7 +2858,7 @@
         <v>64</v>
       </c>
       <c r="F26" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -2881,7 +2881,7 @@
         <v>26</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>57</v>
@@ -2890,7 +2890,7 @@
         <v>64</v>
       </c>
       <c r="F28" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="29" spans="1:6">
@@ -2910,16 +2910,16 @@
         <v>91</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="F30" t="s">
         <v>72</v>
@@ -2931,10 +2931,10 @@
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
       <c r="E31" s="1" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="F31" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="32" spans="1:6">
@@ -2942,16 +2942,16 @@
         <v>92</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="F32" t="s">
         <v>72</v>
@@ -2963,7 +2963,7 @@
       <c r="C33" s="1"/>
       <c r="D33" s="1"/>
       <c r="E33" s="1" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="F33" t="s">
         <v>71</v>
@@ -2974,19 +2974,19 @@
         <v>93</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="D34" s="1" t="s">
         <v>56</v>
       </c>
       <c r="E34" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="F34" t="s">
         <v>320</v>
-      </c>
-      <c r="F34" t="s">
-        <v>326</v>
       </c>
     </row>
     <row r="35" spans="1:6">
@@ -2994,19 +2994,19 @@
         <v>94</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>56</v>
       </c>
       <c r="E35" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="F35" t="s">
         <v>320</v>
-      </c>
-      <c r="F35" t="s">
-        <v>326</v>
       </c>
     </row>
     <row r="36" spans="1:6">
@@ -3014,16 +3014,16 @@
         <v>95</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="F36" t="s">
         <v>72</v>
@@ -3035,10 +3035,10 @@
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
       <c r="E37" s="1" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="F37" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="38" spans="1:6">
@@ -3046,16 +3046,16 @@
         <v>96</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="F38" t="s">
         <v>72</v>
@@ -3067,10 +3067,10 @@
       <c r="C39" s="1"/>
       <c r="D39" s="1"/>
       <c r="E39" s="1" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="F39" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="40" spans="1:6">
@@ -3078,16 +3078,16 @@
         <v>97</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="F40" t="s">
         <v>72</v>
@@ -3099,10 +3099,10 @@
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
       <c r="E41" s="1" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="F41" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="42" spans="1:6">
@@ -3110,16 +3110,16 @@
         <v>98</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="F42" t="s">
         <v>72</v>
@@ -3131,7 +3131,7 @@
       <c r="C43" s="1"/>
       <c r="D43" s="1"/>
       <c r="E43" s="1" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="F43" t="s">
         <v>71</v>
@@ -3142,10 +3142,10 @@
         <v>99</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="D44" s="1" t="s">
         <v>56</v>
@@ -3165,13 +3165,13 @@
         <v>28</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="D45" s="1" t="s">
         <v>56</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="F45" t="s">
         <v>74</v>
@@ -3182,10 +3182,10 @@
         <v>101</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="D46" s="1" t="s">
         <v>56</v>
@@ -3202,13 +3202,13 @@
         <v>102</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="E47" s="1" t="s">
         <v>64</v>
@@ -3234,10 +3234,10 @@
         <v>103</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="D49" s="1" t="s">
         <v>60</v>
@@ -3254,10 +3254,10 @@
         <v>104</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="D50" s="1" t="s">
         <v>60</v>
@@ -3274,10 +3274,10 @@
         <v>105</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="D51" s="1" t="s">
         <v>60</v>
@@ -3294,10 +3294,10 @@
         <v>106</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="D52" s="1" t="s">
         <v>60</v>
@@ -3314,10 +3314,10 @@
         <v>107</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D53" s="1" t="s">
         <v>60</v>
@@ -3334,10 +3334,10 @@
         <v>108</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="D54" s="1" t="s">
         <v>60</v>
@@ -3357,7 +3357,7 @@
         <v>33</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="D55" s="1" t="s">
         <v>61</v>
@@ -3386,10 +3386,10 @@
         <v>110</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>55</v>
@@ -3406,10 +3406,10 @@
         <v>111</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D58" s="1" t="s">
         <v>55</v>
@@ -3418,7 +3418,7 @@
         <v>64</v>
       </c>
       <c r="F58" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="59" spans="1:6">
@@ -3438,16 +3438,16 @@
         <v>112</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="D60" s="1" t="s">
         <v>58</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="F60" t="s">
         <v>72</v>
@@ -3459,10 +3459,10 @@
       <c r="C61" s="1"/>
       <c r="D61" s="1"/>
       <c r="E61" s="1" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="F61" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="62" spans="1:6">
@@ -3470,19 +3470,19 @@
         <v>113</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="D62" s="1" t="s">
         <v>56</v>
       </c>
       <c r="E62" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="F62" t="s">
         <v>320</v>
-      </c>
-      <c r="F62" t="s">
-        <v>326</v>
       </c>
     </row>
     <row r="63" spans="1:6">
@@ -3490,16 +3490,16 @@
         <v>114</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="F63" t="s">
         <v>72</v>
@@ -3511,10 +3511,10 @@
       <c r="C64" s="1"/>
       <c r="D64" s="1"/>
       <c r="E64" s="1" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="F64" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -3522,16 +3522,16 @@
         <v>115</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="F65" t="s">
         <v>74</v>
@@ -3543,7 +3543,7 @@
       <c r="C66" s="1"/>
       <c r="D66" s="1"/>
       <c r="E66" s="1" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="F66" t="s">
         <v>75</v>
@@ -3557,7 +3557,7 @@
         <v>35</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="D67" s="1" t="s">
         <v>62</v>
@@ -3566,7 +3566,7 @@
         <v>64</v>
       </c>
       <c r="F67" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="68" spans="1:6">
@@ -3589,7 +3589,7 @@
         <v>35</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="D69" s="1" t="s">
         <v>62</v>
@@ -3598,7 +3598,7 @@
         <v>64</v>
       </c>
       <c r="F69" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="70" spans="1:6">
@@ -3621,7 +3621,7 @@
         <v>35</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="D71" s="1" t="s">
         <v>62</v>
@@ -3630,7 +3630,7 @@
         <v>64</v>
       </c>
       <c r="F71" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="72" spans="1:6">
@@ -3653,7 +3653,7 @@
         <v>35</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="D73" s="1" t="s">
         <v>62</v>
@@ -3662,7 +3662,7 @@
         <v>64</v>
       </c>
       <c r="F73" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="74" spans="1:6">
@@ -3685,7 +3685,7 @@
         <v>35</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="D75" s="1" t="s">
         <v>62</v>
@@ -3694,7 +3694,7 @@
         <v>64</v>
       </c>
       <c r="F75" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="76" spans="1:6">
@@ -3717,7 +3717,7 @@
         <v>35</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="D77" s="1" t="s">
         <v>62</v>
@@ -3726,7 +3726,7 @@
         <v>64</v>
       </c>
       <c r="F77" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="78" spans="1:6">
@@ -3749,7 +3749,7 @@
         <v>35</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="D79" s="1" t="s">
         <v>62</v>
@@ -3781,7 +3781,7 @@
         <v>35</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="D81" s="1" t="s">
         <v>62</v>
@@ -3790,7 +3790,7 @@
         <v>64</v>
       </c>
       <c r="F81" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="82" spans="1:6">
@@ -3813,7 +3813,7 @@
         <v>35</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="D83" s="1" t="s">
         <v>62</v>
@@ -3822,7 +3822,7 @@
         <v>64</v>
       </c>
       <c r="F83" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="84" spans="1:6">
@@ -3845,7 +3845,7 @@
         <v>35</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D85" s="1" t="s">
         <v>62</v>
@@ -3854,7 +3854,7 @@
         <v>64</v>
       </c>
       <c r="F85" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="86" spans="1:6">
@@ -3877,7 +3877,7 @@
         <v>35</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="D87" s="1" t="s">
         <v>62</v>
@@ -3886,7 +3886,7 @@
         <v>64</v>
       </c>
       <c r="F87" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="88" spans="1:6">
@@ -3906,10 +3906,10 @@
         <v>127</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="D89" s="1" t="s">
         <v>59</v>
@@ -3926,10 +3926,10 @@
         <v>128</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="D90" s="1" t="s">
         <v>59</v>
@@ -3946,10 +3946,10 @@
         <v>129</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="D91" s="1" t="s">
         <v>62</v>
@@ -3978,16 +3978,16 @@
         <v>130</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="D93" s="1" t="s">
         <v>62</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="F93" t="s">
         <v>72</v>
@@ -3999,10 +3999,10 @@
       <c r="C94" s="1"/>
       <c r="D94" s="1"/>
       <c r="E94" s="1" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="F94" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="95" spans="1:6">
@@ -4013,7 +4013,7 @@
         <v>36</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="D95" s="1" t="s">
         <v>61</v>
@@ -4022,7 +4022,7 @@
         <v>64</v>
       </c>
       <c r="F95" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="96" spans="1:6">
@@ -4045,7 +4045,7 @@
         <v>36</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="D97" s="1" t="s">
         <v>61</v>
@@ -4077,7 +4077,7 @@
         <v>36</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="D99" s="1" t="s">
         <v>61</v>
@@ -4109,7 +4109,7 @@
         <v>36</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="D101" s="1" t="s">
         <v>61</v>
@@ -4118,7 +4118,7 @@
         <v>64</v>
       </c>
       <c r="F101" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="102" spans="1:6">
@@ -4141,7 +4141,7 @@
         <v>36</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="D103" s="1" t="s">
         <v>61</v>
@@ -4150,7 +4150,7 @@
         <v>64</v>
       </c>
       <c r="F103" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="104" spans="1:6">
@@ -4173,7 +4173,7 @@
         <v>36</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="D105" s="1" t="s">
         <v>61</v>
@@ -4182,7 +4182,7 @@
         <v>64</v>
       </c>
       <c r="F105" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="106" spans="1:6">
@@ -4205,7 +4205,7 @@
         <v>36</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="D107" s="1" t="s">
         <v>61</v>
@@ -4214,7 +4214,7 @@
         <v>64</v>
       </c>
       <c r="F107" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="108" spans="1:6">
@@ -4237,7 +4237,7 @@
         <v>36</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="D109" s="1" t="s">
         <v>61</v>
@@ -4246,7 +4246,7 @@
         <v>64</v>
       </c>
       <c r="F109" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="110" spans="1:6">
@@ -4269,7 +4269,7 @@
         <v>36</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="D111" s="1" t="s">
         <v>61</v>
@@ -4301,7 +4301,7 @@
         <v>36</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="D113" s="1" t="s">
         <v>61</v>
@@ -4310,7 +4310,7 @@
         <v>64</v>
       </c>
       <c r="F113" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="114" spans="1:6">
@@ -4333,7 +4333,7 @@
         <v>36</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="D115" s="1" t="s">
         <v>61</v>
@@ -4342,7 +4342,7 @@
         <v>64</v>
       </c>
       <c r="F115" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="116" spans="1:6">
@@ -4365,7 +4365,7 @@
         <v>36</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="D117" s="1" t="s">
         <v>61</v>
@@ -4374,7 +4374,7 @@
         <v>64</v>
       </c>
       <c r="F117" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="118" spans="1:6">
@@ -4397,7 +4397,7 @@
         <v>36</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="D119" s="1" t="s">
         <v>61</v>
@@ -4406,7 +4406,7 @@
         <v>64</v>
       </c>
       <c r="F119" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="120" spans="1:6">
@@ -4429,7 +4429,7 @@
         <v>37</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="D121" s="1" t="s">
         <v>61</v>
@@ -4438,7 +4438,7 @@
         <v>64</v>
       </c>
       <c r="F121" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="122" spans="1:6">
@@ -4461,7 +4461,7 @@
         <v>37</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="D123" s="1" t="s">
         <v>61</v>
@@ -4493,7 +4493,7 @@
         <v>37</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="D125" s="1" t="s">
         <v>61</v>
@@ -4525,7 +4525,7 @@
         <v>37</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="D127" s="1" t="s">
         <v>61</v>
@@ -4534,7 +4534,7 @@
         <v>64</v>
       </c>
       <c r="F127" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="128" spans="1:6">
@@ -4557,7 +4557,7 @@
         <v>37</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="D129" s="1" t="s">
         <v>61</v>
@@ -4566,7 +4566,7 @@
         <v>64</v>
       </c>
       <c r="F129" t="s">
-        <v>71</v>
+        <v>319</v>
       </c>
     </row>
     <row r="130" spans="1:6">
@@ -4589,7 +4589,7 @@
         <v>37</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="D131" s="1" t="s">
         <v>61</v>
@@ -4598,7 +4598,7 @@
         <v>64</v>
       </c>
       <c r="F131" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="132" spans="1:6">
@@ -4621,7 +4621,7 @@
         <v>37</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="D133" s="1" t="s">
         <v>61</v>
@@ -4630,7 +4630,7 @@
         <v>64</v>
       </c>
       <c r="F133" t="s">
-        <v>71</v>
+        <v>319</v>
       </c>
     </row>
     <row r="134" spans="1:6">
@@ -4653,7 +4653,7 @@
         <v>37</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="D135" s="1" t="s">
         <v>61</v>
@@ -4662,7 +4662,7 @@
         <v>64</v>
       </c>
       <c r="F135" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="136" spans="1:6">
@@ -4685,7 +4685,7 @@
         <v>37</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="D137" s="1" t="s">
         <v>61</v>
@@ -4717,7 +4717,7 @@
         <v>37</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="D139" s="1" t="s">
         <v>61</v>
@@ -4726,7 +4726,7 @@
         <v>64</v>
       </c>
       <c r="F139" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="140" spans="1:6">
@@ -4749,7 +4749,7 @@
         <v>37</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="D141" s="1" t="s">
         <v>61</v>
@@ -4758,7 +4758,7 @@
         <v>64</v>
       </c>
       <c r="F141" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="142" spans="1:6">
@@ -4781,7 +4781,7 @@
         <v>37</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="D143" s="1" t="s">
         <v>61</v>
@@ -4790,7 +4790,7 @@
         <v>64</v>
       </c>
       <c r="F143" t="s">
-        <v>71</v>
+        <v>319</v>
       </c>
     </row>
     <row r="144" spans="1:6">
@@ -4813,7 +4813,7 @@
         <v>37</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="D145" s="1" t="s">
         <v>61</v>
@@ -4822,7 +4822,7 @@
         <v>64</v>
       </c>
       <c r="F145" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="146" spans="1:6">
@@ -4842,10 +4842,10 @@
         <v>157</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>37</v>
+        <v>207</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="D147" s="1" t="s">
         <v>61</v>
@@ -4854,7 +4854,7 @@
         <v>64</v>
       </c>
       <c r="F147" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="148" spans="1:6">
@@ -4874,10 +4874,10 @@
         <v>158</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>37</v>
+        <v>207</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="D149" s="1" t="s">
         <v>61</v>
@@ -4886,7 +4886,7 @@
         <v>64</v>
       </c>
       <c r="F149" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="150" spans="1:6">
@@ -4906,10 +4906,10 @@
         <v>159</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>37</v>
+        <v>207</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="D151" s="1" t="s">
         <v>61</v>
@@ -4918,7 +4918,7 @@
         <v>64</v>
       </c>
       <c r="F151" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="152" spans="1:6">
@@ -4938,10 +4938,10 @@
         <v>160</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="D153" s="1" t="s">
         <v>61</v>
@@ -4950,7 +4950,7 @@
         <v>64</v>
       </c>
       <c r="F153" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="154" spans="1:6">
@@ -4970,10 +4970,10 @@
         <v>161</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="D155" s="1" t="s">
         <v>61</v>
@@ -4982,7 +4982,7 @@
         <v>64</v>
       </c>
       <c r="F155" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="156" spans="1:6">
@@ -5002,10 +5002,10 @@
         <v>162</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="D157" s="1" t="s">
         <v>61</v>
@@ -5014,7 +5014,7 @@
         <v>64</v>
       </c>
       <c r="F157" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="158" spans="1:6">
@@ -5034,10 +5034,10 @@
         <v>163</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="D159" s="1" t="s">
         <v>61</v>
@@ -5046,7 +5046,7 @@
         <v>64</v>
       </c>
       <c r="F159" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="160" spans="1:6">
@@ -5066,10 +5066,10 @@
         <v>164</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="C161" s="1" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="D161" s="1" t="s">
         <v>61</v>
@@ -5078,7 +5078,7 @@
         <v>64</v>
       </c>
       <c r="F161" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="162" spans="1:6">
@@ -5098,10 +5098,10 @@
         <v>165</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="C163" s="1" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="D163" s="1" t="s">
         <v>61</v>
@@ -5110,7 +5110,7 @@
         <v>64</v>
       </c>
       <c r="F163" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="164" spans="1:6">
@@ -5130,10 +5130,10 @@
         <v>166</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="C165" s="1" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="D165" s="1" t="s">
         <v>61</v>
@@ -5142,7 +5142,7 @@
         <v>64</v>
       </c>
       <c r="F165" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="166" spans="1:6">
@@ -5162,19 +5162,19 @@
         <v>167</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C167" s="1" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E167" s="1" t="s">
         <v>64</v>
       </c>
       <c r="F167" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="168" spans="1:6">
@@ -5194,19 +5194,19 @@
         <v>168</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C169" s="1" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E169" s="1" t="s">
         <v>64</v>
       </c>
       <c r="F169" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="170" spans="1:6">
@@ -5226,19 +5226,19 @@
         <v>169</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C171" s="1" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E171" s="1" t="s">
         <v>64</v>
       </c>
       <c r="F171" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="172" spans="1:6">
@@ -5258,10 +5258,10 @@
         <v>170</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="C173" s="1" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="D173" s="1" t="s">
         <v>58</v>
@@ -5270,7 +5270,7 @@
         <v>64</v>
       </c>
       <c r="F173" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="174" spans="1:6">
@@ -5290,10 +5290,10 @@
         <v>171</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="C175" s="1" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="D175" s="1" t="s">
         <v>58</v>
@@ -5302,7 +5302,7 @@
         <v>64</v>
       </c>
       <c r="F175" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="176" spans="1:6">
@@ -5322,10 +5322,10 @@
         <v>172</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="C177" s="1" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="D177" s="1" t="s">
         <v>58</v>
@@ -5334,7 +5334,7 @@
         <v>64</v>
       </c>
       <c r="F177" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="178" spans="1:6">
@@ -5354,10 +5354,10 @@
         <v>173</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="C179" s="1" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="D179" s="1" t="s">
         <v>58</v>
@@ -5366,7 +5366,7 @@
         <v>64</v>
       </c>
       <c r="F179" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="180" spans="1:6">
@@ -5386,10 +5386,10 @@
         <v>174</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="C181" s="1" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="D181" s="1" t="s">
         <v>58</v>
@@ -5398,7 +5398,7 @@
         <v>64</v>
       </c>
       <c r="F181" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="182" spans="1:6">
@@ -5418,10 +5418,10 @@
         <v>175</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="C183" s="1" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="D183" s="1" t="s">
         <v>58</v>
@@ -5430,7 +5430,7 @@
         <v>64</v>
       </c>
       <c r="F183" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="184" spans="1:6">
@@ -5450,10 +5450,10 @@
         <v>176</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="C185" s="1" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="D185" s="1" t="s">
         <v>58</v>
@@ -5462,7 +5462,7 @@
         <v>64</v>
       </c>
       <c r="F185" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="186" spans="1:6">
@@ -5482,10 +5482,10 @@
         <v>177</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C187" s="1" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="D187" s="1" t="s">
         <v>58</v>
@@ -5494,7 +5494,7 @@
         <v>64</v>
       </c>
       <c r="F187" t="s">
-        <v>325</v>
+        <v>71</v>
       </c>
     </row>
     <row r="188" spans="1:6">
@@ -5509,104 +5509,8 @@
         <v>72</v>
       </c>
     </row>
-    <row r="189" spans="1:6">
-      <c r="A189" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="B189" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="C189" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="D189" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="E189" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="F189" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="190" spans="1:6">
-      <c r="A190" s="1"/>
-      <c r="B190" s="1"/>
-      <c r="C190" s="1"/>
-      <c r="D190" s="1"/>
-      <c r="E190" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="F190" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="191" spans="1:6">
-      <c r="A191" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="B191" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="C191" s="1" t="s">
-        <v>316</v>
-      </c>
-      <c r="D191" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="E191" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="F191" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="192" spans="1:6">
-      <c r="A192" s="1"/>
-      <c r="B192" s="1"/>
-      <c r="C192" s="1"/>
-      <c r="D192" s="1"/>
-      <c r="E192" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="F192" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="193" spans="1:6">
-      <c r="A193" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="B193" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="C193" s="1" t="s">
-        <v>317</v>
-      </c>
-      <c r="D193" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="E193" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="F193" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="194" spans="1:6">
-      <c r="A194" s="1"/>
-      <c r="B194" s="1"/>
-      <c r="C194" s="1"/>
-      <c r="D194" s="1"/>
-      <c r="E194" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="F194" t="s">
-        <v>72</v>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="352">
+  <mergeCells count="340">
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="A8:A9"/>
@@ -5692,9 +5596,6 @@
     <mergeCell ref="A183:A184"/>
     <mergeCell ref="A185:A186"/>
     <mergeCell ref="A187:A188"/>
-    <mergeCell ref="A189:A190"/>
-    <mergeCell ref="A191:A192"/>
-    <mergeCell ref="A193:A194"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="B4:B5"/>
     <mergeCell ref="B8:B9"/>
@@ -5780,9 +5681,6 @@
     <mergeCell ref="B183:B184"/>
     <mergeCell ref="B185:B186"/>
     <mergeCell ref="B187:B188"/>
-    <mergeCell ref="B189:B190"/>
-    <mergeCell ref="B191:B192"/>
-    <mergeCell ref="B193:B194"/>
     <mergeCell ref="C2:C3"/>
     <mergeCell ref="C4:C5"/>
     <mergeCell ref="C8:C9"/>
@@ -5868,9 +5766,6 @@
     <mergeCell ref="C183:C184"/>
     <mergeCell ref="C185:C186"/>
     <mergeCell ref="C187:C188"/>
-    <mergeCell ref="C189:C190"/>
-    <mergeCell ref="C191:C192"/>
-    <mergeCell ref="C193:C194"/>
     <mergeCell ref="D2:D3"/>
     <mergeCell ref="D4:D5"/>
     <mergeCell ref="D8:D9"/>
@@ -5956,9 +5851,6 @@
     <mergeCell ref="D183:D184"/>
     <mergeCell ref="D185:D186"/>
     <mergeCell ref="D187:D188"/>
-    <mergeCell ref="D189:D190"/>
-    <mergeCell ref="D191:D192"/>
-    <mergeCell ref="D193:D194"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5966,7 +5858,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F136"/>
+  <dimension ref="A1:F142"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="6" width="40.7109375" customWidth="1"/>
@@ -5994,13 +5886,13 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="1" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>501</v>
@@ -6014,13 +5906,13 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="1" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>502</v>
@@ -6046,13 +5938,13 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="1" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>502</v>
@@ -6078,13 +5970,13 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="1" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>502</v>
@@ -6110,13 +6002,13 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="1" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>502</v>
@@ -6142,13 +6034,13 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="1" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>55</v>
@@ -6157,18 +6049,18 @@
         <v>63</v>
       </c>
       <c r="F11" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="1" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>55</v>
@@ -6177,18 +6069,18 @@
         <v>63</v>
       </c>
       <c r="F12" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="1" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>55</v>
@@ -6197,18 +6089,18 @@
         <v>63</v>
       </c>
       <c r="F13" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="1" t="s">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>58</v>
@@ -6222,19 +6114,19 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="1" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>56</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="F15" t="s">
         <v>70</v>
@@ -6242,13 +6134,13 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="1" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>57</v>
@@ -6257,7 +6149,7 @@
         <v>64</v>
       </c>
       <c r="F16" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -6274,13 +6166,13 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="1" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>57</v>
@@ -6289,7 +6181,7 @@
         <v>64</v>
       </c>
       <c r="F18" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -6306,13 +6198,13 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="1" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>57</v>
@@ -6321,7 +6213,7 @@
         <v>64</v>
       </c>
       <c r="F20" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -6338,13 +6230,13 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="1" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>57</v>
@@ -6353,7 +6245,7 @@
         <v>64</v>
       </c>
       <c r="F22" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -6370,13 +6262,13 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="1" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>57</v>
@@ -6385,7 +6277,7 @@
         <v>64</v>
       </c>
       <c r="F24" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -6402,13 +6294,13 @@
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="1" t="s">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>57</v>
@@ -6417,7 +6309,7 @@
         <v>64</v>
       </c>
       <c r="F26" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -6434,13 +6326,13 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="1" t="s">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>57</v>
@@ -6449,7 +6341,7 @@
         <v>64</v>
       </c>
       <c r="F28" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="29" spans="1:6">
@@ -6466,13 +6358,13 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="1" t="s">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>57</v>
@@ -6481,7 +6373,7 @@
         <v>64</v>
       </c>
       <c r="F30" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="31" spans="1:6">
@@ -6498,13 +6390,13 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="1" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>62</v>
@@ -6530,13 +6422,13 @@
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="1" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="D34" s="1" t="s">
         <v>62</v>
@@ -6562,16 +6454,16 @@
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="1" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="E36" s="1" t="s">
         <v>504</v>
@@ -6582,13 +6474,13 @@
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="1" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="D37" s="1" t="s">
         <v>57</v>
@@ -6602,13 +6494,13 @@
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="1" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="D38" s="1" t="s">
         <v>60</v>
@@ -6617,18 +6509,18 @@
         <v>63</v>
       </c>
       <c r="F38" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
     </row>
     <row r="39" spans="1:6">
       <c r="A39" s="1" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="D39" s="1" t="s">
         <v>60</v>
@@ -6637,18 +6529,18 @@
         <v>63</v>
       </c>
       <c r="F39" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
     </row>
     <row r="40" spans="1:6">
       <c r="A40" s="1" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="D40" s="1" t="s">
         <v>60</v>
@@ -6657,18 +6549,18 @@
         <v>63</v>
       </c>
       <c r="F40" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
     </row>
     <row r="41" spans="1:6">
       <c r="A41" s="1" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="D41" s="1" t="s">
         <v>58</v>
@@ -6682,13 +6574,13 @@
     </row>
     <row r="42" spans="1:6">
       <c r="A42" s="1" t="s">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="D42" s="1" t="s">
         <v>60</v>
@@ -6697,18 +6589,18 @@
         <v>63</v>
       </c>
       <c r="F42" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
     </row>
     <row r="43" spans="1:6">
       <c r="A43" s="1" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>60</v>
@@ -6717,18 +6609,18 @@
         <v>63</v>
       </c>
       <c r="F43" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
     </row>
     <row r="44" spans="1:6">
       <c r="A44" s="1" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="D44" s="1" t="s">
         <v>60</v>
@@ -6737,18 +6629,18 @@
         <v>63</v>
       </c>
       <c r="F44" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
     </row>
     <row r="45" spans="1:6">
       <c r="A45" s="1" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="D45" s="1" t="s">
         <v>55</v>
@@ -6762,13 +6654,13 @@
     </row>
     <row r="46" spans="1:6">
       <c r="A46" s="1" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="D46" s="1" t="s">
         <v>55</v>
@@ -6782,13 +6674,13 @@
     </row>
     <row r="47" spans="1:6">
       <c r="A47" s="1" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="D47" s="1" t="s">
         <v>55</v>
@@ -6802,13 +6694,13 @@
     </row>
     <row r="48" spans="1:6">
       <c r="A48" s="1" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>35</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="D48" s="1" t="s">
         <v>62</v>
@@ -6817,7 +6709,7 @@
         <v>64</v>
       </c>
       <c r="F48" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="49" spans="1:6">
@@ -6834,13 +6726,13 @@
     </row>
     <row r="50" spans="1:6">
       <c r="A50" s="1" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>35</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="D50" s="1" t="s">
         <v>62</v>
@@ -6849,7 +6741,7 @@
         <v>64</v>
       </c>
       <c r="F50" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="51" spans="1:6">
@@ -6866,13 +6758,13 @@
     </row>
     <row r="52" spans="1:6">
       <c r="A52" s="1" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>35</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="D52" s="1" t="s">
         <v>62</v>
@@ -6881,7 +6773,7 @@
         <v>64</v>
       </c>
       <c r="F52" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="53" spans="1:6">
@@ -6898,13 +6790,13 @@
     </row>
     <row r="54" spans="1:6">
       <c r="A54" s="1" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>35</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="D54" s="1" t="s">
         <v>62</v>
@@ -6913,7 +6805,7 @@
         <v>64</v>
       </c>
       <c r="F54" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="55" spans="1:6">
@@ -6930,13 +6822,13 @@
     </row>
     <row r="56" spans="1:6">
       <c r="A56" s="1" t="s">
-        <v>363</v>
+        <v>357</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>35</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="D56" s="1" t="s">
         <v>62</v>
@@ -6945,7 +6837,7 @@
         <v>64</v>
       </c>
       <c r="F56" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="57" spans="1:6">
@@ -6962,13 +6854,13 @@
     </row>
     <row r="58" spans="1:6">
       <c r="A58" s="1" t="s">
-        <v>364</v>
+        <v>358</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>35</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="D58" s="1" t="s">
         <v>62</v>
@@ -6977,7 +6869,7 @@
         <v>64</v>
       </c>
       <c r="F58" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="59" spans="1:6">
@@ -6994,13 +6886,13 @@
     </row>
     <row r="60" spans="1:6">
       <c r="A60" s="1" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>35</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="D60" s="1" t="s">
         <v>62</v>
@@ -7009,7 +6901,7 @@
         <v>64</v>
       </c>
       <c r="F60" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="61" spans="1:6">
@@ -7026,13 +6918,13 @@
     </row>
     <row r="62" spans="1:6">
       <c r="A62" s="1" t="s">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>35</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="D62" s="1" t="s">
         <v>62</v>
@@ -7041,7 +6933,7 @@
         <v>64</v>
       </c>
       <c r="F62" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="63" spans="1:6">
@@ -7058,13 +6950,13 @@
     </row>
     <row r="64" spans="1:6">
       <c r="A64" s="1" t="s">
-        <v>367</v>
+        <v>361</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>36</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="D64" s="1" t="s">
         <v>61</v>
@@ -7073,7 +6965,7 @@
         <v>64</v>
       </c>
       <c r="F64" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -7090,13 +6982,13 @@
     </row>
     <row r="66" spans="1:6">
       <c r="A66" s="1" t="s">
-        <v>368</v>
+        <v>362</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>36</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="D66" s="1" t="s">
         <v>61</v>
@@ -7105,7 +6997,7 @@
         <v>64</v>
       </c>
       <c r="F66" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="67" spans="1:6">
@@ -7122,13 +7014,13 @@
     </row>
     <row r="68" spans="1:6">
       <c r="A68" s="1" t="s">
-        <v>369</v>
+        <v>363</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>36</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="D68" s="1" t="s">
         <v>61</v>
@@ -7137,7 +7029,7 @@
         <v>64</v>
       </c>
       <c r="F68" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="69" spans="1:6">
@@ -7154,13 +7046,13 @@
     </row>
     <row r="70" spans="1:6">
       <c r="A70" s="1" t="s">
-        <v>370</v>
+        <v>364</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>36</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="D70" s="1" t="s">
         <v>61</v>
@@ -7169,7 +7061,7 @@
         <v>64</v>
       </c>
       <c r="F70" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="71" spans="1:6">
@@ -7186,13 +7078,13 @@
     </row>
     <row r="72" spans="1:6">
       <c r="A72" s="1" t="s">
-        <v>371</v>
+        <v>365</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>36</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="D72" s="1" t="s">
         <v>61</v>
@@ -7218,13 +7110,13 @@
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="1" t="s">
-        <v>372</v>
+        <v>366</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>36</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="D74" s="1" t="s">
         <v>61</v>
@@ -7250,13 +7142,13 @@
     </row>
     <row r="76" spans="1:6">
       <c r="A76" s="1" t="s">
-        <v>373</v>
+        <v>367</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>36</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="D76" s="1" t="s">
         <v>61</v>
@@ -7265,7 +7157,7 @@
         <v>64</v>
       </c>
       <c r="F76" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="77" spans="1:6">
@@ -7282,13 +7174,13 @@
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="1" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>36</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="D78" s="1" t="s">
         <v>61</v>
@@ -7314,13 +7206,13 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="1" t="s">
-        <v>375</v>
+        <v>369</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>36</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="D80" s="1" t="s">
         <v>61</v>
@@ -7329,7 +7221,7 @@
         <v>64</v>
       </c>
       <c r="F80" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="81" spans="1:6">
@@ -7346,13 +7238,13 @@
     </row>
     <row r="82" spans="1:6">
       <c r="A82" s="1" t="s">
-        <v>376</v>
+        <v>370</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>36</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="D82" s="1" t="s">
         <v>61</v>
@@ -7361,7 +7253,7 @@
         <v>64</v>
       </c>
       <c r="F82" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="83" spans="1:6">
@@ -7378,13 +7270,13 @@
     </row>
     <row r="84" spans="1:6">
       <c r="A84" s="1" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>36</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="D84" s="1" t="s">
         <v>61</v>
@@ -7393,7 +7285,7 @@
         <v>64</v>
       </c>
       <c r="F84" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="85" spans="1:6">
@@ -7410,13 +7302,13 @@
     </row>
     <row r="86" spans="1:6">
       <c r="A86" s="1" t="s">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>37</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="D86" s="1" t="s">
         <v>61</v>
@@ -7425,7 +7317,7 @@
         <v>64</v>
       </c>
       <c r="F86" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="87" spans="1:6">
@@ -7442,13 +7334,13 @@
     </row>
     <row r="88" spans="1:6">
       <c r="A88" s="1" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>37</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="D88" s="1" t="s">
         <v>61</v>
@@ -7457,7 +7349,7 @@
         <v>64</v>
       </c>
       <c r="F88" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="89" spans="1:6">
@@ -7474,13 +7366,13 @@
     </row>
     <row r="90" spans="1:6">
       <c r="A90" s="1" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>37</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="D90" s="1" t="s">
         <v>61</v>
@@ -7489,7 +7381,7 @@
         <v>64</v>
       </c>
       <c r="F90" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="91" spans="1:6">
@@ -7506,13 +7398,13 @@
     </row>
     <row r="92" spans="1:6">
       <c r="A92" s="1" t="s">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>37</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="D92" s="1" t="s">
         <v>61</v>
@@ -7521,7 +7413,7 @@
         <v>64</v>
       </c>
       <c r="F92" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="93" spans="1:6">
@@ -7538,13 +7430,13 @@
     </row>
     <row r="94" spans="1:6">
       <c r="A94" s="1" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>37</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="D94" s="1" t="s">
         <v>61</v>
@@ -7553,7 +7445,7 @@
         <v>64</v>
       </c>
       <c r="F94" t="s">
-        <v>325</v>
+        <v>71</v>
       </c>
     </row>
     <row r="95" spans="1:6">
@@ -7570,13 +7462,13 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="1" t="s">
-        <v>383</v>
+        <v>377</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>37</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="D96" s="1" t="s">
         <v>61</v>
@@ -7585,7 +7477,7 @@
         <v>64</v>
       </c>
       <c r="F96" t="s">
-        <v>325</v>
+        <v>71</v>
       </c>
     </row>
     <row r="97" spans="1:6">
@@ -7602,13 +7494,13 @@
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="1" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>37</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="D98" s="1" t="s">
         <v>61</v>
@@ -7617,7 +7509,7 @@
         <v>64</v>
       </c>
       <c r="F98" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="99" spans="1:6">
@@ -7634,13 +7526,13 @@
     </row>
     <row r="100" spans="1:6">
       <c r="A100" s="1" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>37</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="D100" s="1" t="s">
         <v>61</v>
@@ -7649,7 +7541,7 @@
         <v>64</v>
       </c>
       <c r="F100" t="s">
-        <v>325</v>
+        <v>71</v>
       </c>
     </row>
     <row r="101" spans="1:6">
@@ -7666,13 +7558,13 @@
     </row>
     <row r="102" spans="1:6">
       <c r="A102" s="1" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>210</v>
+        <v>37</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="D102" s="1" t="s">
         <v>61</v>
@@ -7681,7 +7573,7 @@
         <v>64</v>
       </c>
       <c r="F102" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="103" spans="1:6">
@@ -7698,13 +7590,13 @@
     </row>
     <row r="104" spans="1:6">
       <c r="A104" s="1" t="s">
-        <v>387</v>
+        <v>381</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>210</v>
+        <v>37</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="D104" s="1" t="s">
         <v>61</v>
@@ -7713,7 +7605,7 @@
         <v>64</v>
       </c>
       <c r="F104" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="105" spans="1:6">
@@ -7730,13 +7622,13 @@
     </row>
     <row r="106" spans="1:6">
       <c r="A106" s="1" t="s">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>210</v>
+        <v>37</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="D106" s="1" t="s">
         <v>61</v>
@@ -7745,7 +7637,7 @@
         <v>64</v>
       </c>
       <c r="F106" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="107" spans="1:6">
@@ -7762,13 +7654,13 @@
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="1" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="D108" s="1" t="s">
         <v>61</v>
@@ -7777,7 +7669,7 @@
         <v>64</v>
       </c>
       <c r="F108" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="109" spans="1:6">
@@ -7794,13 +7686,13 @@
     </row>
     <row r="110" spans="1:6">
       <c r="A110" s="1" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="D110" s="1" t="s">
         <v>61</v>
@@ -7809,7 +7701,7 @@
         <v>64</v>
       </c>
       <c r="F110" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="111" spans="1:6">
@@ -7826,13 +7718,13 @@
     </row>
     <row r="112" spans="1:6">
       <c r="A112" s="1" t="s">
-        <v>391</v>
+        <v>385</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="D112" s="1" t="s">
         <v>61</v>
@@ -7841,7 +7733,7 @@
         <v>64</v>
       </c>
       <c r="F112" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="113" spans="1:6">
@@ -7858,13 +7750,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="1" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="D114" s="1" t="s">
         <v>61</v>
@@ -7873,7 +7765,7 @@
         <v>64</v>
       </c>
       <c r="F114" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="115" spans="1:6">
@@ -7890,13 +7782,13 @@
     </row>
     <row r="116" spans="1:6">
       <c r="A116" s="1" t="s">
-        <v>393</v>
+        <v>387</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="D116" s="1" t="s">
         <v>61</v>
@@ -7905,7 +7797,7 @@
         <v>64</v>
       </c>
       <c r="F116" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="117" spans="1:6">
@@ -7922,22 +7814,22 @@
     </row>
     <row r="118" spans="1:6">
       <c r="A118" s="1" t="s">
-        <v>394</v>
+        <v>388</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>422</v>
+        <v>207</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="D118" s="1" t="s">
         <v>61</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F118" t="s">
-        <v>74</v>
+        <v>319</v>
       </c>
     </row>
     <row r="119" spans="1:6">
@@ -7946,121 +7838,121 @@
       <c r="C119" s="1"/>
       <c r="D119" s="1"/>
       <c r="E119" s="1" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F119" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="120" spans="1:6">
       <c r="A120" s="1" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>423</v>
+        <v>207</v>
       </c>
       <c r="C120" s="1" t="s">
+        <v>489</v>
+      </c>
+      <c r="D120" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E120" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F120" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6">
+      <c r="A121" s="1"/>
+      <c r="B121" s="1"/>
+      <c r="C121" s="1"/>
+      <c r="D121" s="1"/>
+      <c r="E121" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="F121" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6">
+      <c r="A122" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="B122" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="C122" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="D122" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E122" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F122" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6">
+      <c r="A123" s="1"/>
+      <c r="B123" s="1"/>
+      <c r="C123" s="1"/>
+      <c r="D123" s="1"/>
+      <c r="E123" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="F123" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6">
+      <c r="A124" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="B124" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="C124" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="D124" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E124" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="F124" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6">
+      <c r="A125" s="1"/>
+      <c r="B125" s="1"/>
+      <c r="C125" s="1"/>
+      <c r="D125" s="1"/>
+      <c r="E125" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="F125" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6">
+      <c r="A126" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="B126" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="C126" s="1" t="s">
         <v>492</v>
       </c>
-      <c r="D120" s="1" t="s">
+      <c r="D126" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="E120" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="F120" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="121" spans="1:6">
-      <c r="A121" s="1" t="s">
-        <v>396</v>
-      </c>
-      <c r="B121" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="C121" s="1" t="s">
-        <v>493</v>
-      </c>
-      <c r="D121" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="E121" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="F121" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="122" spans="1:6">
-      <c r="A122" s="1"/>
-      <c r="B122" s="1"/>
-      <c r="C122" s="1"/>
-      <c r="D122" s="1"/>
-      <c r="E122" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="F122" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="123" spans="1:6">
-      <c r="A123" s="1" t="s">
-        <v>397</v>
-      </c>
-      <c r="B123" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="C123" s="1" t="s">
-        <v>494</v>
-      </c>
-      <c r="D123" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="E123" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="F123" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="124" spans="1:6">
-      <c r="A124" s="1"/>
-      <c r="B124" s="1"/>
-      <c r="C124" s="1"/>
-      <c r="D124" s="1"/>
-      <c r="E124" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="F124" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="125" spans="1:6">
-      <c r="A125" s="1" t="s">
-        <v>398</v>
-      </c>
-      <c r="B125" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="C125" s="1" t="s">
-        <v>495</v>
-      </c>
-      <c r="D125" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="E125" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="F125" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="126" spans="1:6">
-      <c r="A126" s="1"/>
-      <c r="B126" s="1"/>
-      <c r="C126" s="1"/>
-      <c r="D126" s="1"/>
       <c r="E126" s="1" t="s">
         <v>63</v>
       </c>
@@ -8070,13 +7962,13 @@
     </row>
     <row r="127" spans="1:6">
       <c r="A127" s="1" t="s">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="D127" s="1" t="s">
         <v>58</v>
@@ -8085,7 +7977,7 @@
         <v>64</v>
       </c>
       <c r="F127" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="128" spans="1:6">
@@ -8102,13 +7994,13 @@
     </row>
     <row r="129" spans="1:6">
       <c r="A129" s="1" t="s">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="D129" s="1" t="s">
         <v>58</v>
@@ -8117,7 +8009,7 @@
         <v>64</v>
       </c>
       <c r="F129" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="130" spans="1:6">
@@ -8134,13 +8026,13 @@
     </row>
     <row r="131" spans="1:6">
       <c r="A131" s="1" t="s">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="D131" s="1" t="s">
         <v>58</v>
@@ -8149,7 +8041,7 @@
         <v>64</v>
       </c>
       <c r="F131" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="132" spans="1:6">
@@ -8166,13 +8058,13 @@
     </row>
     <row r="133" spans="1:6">
       <c r="A133" s="1" t="s">
-        <v>402</v>
+        <v>396</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="D133" s="1" t="s">
         <v>58</v>
@@ -8181,7 +8073,7 @@
         <v>64</v>
       </c>
       <c r="F133" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="134" spans="1:6">
@@ -8198,13 +8090,13 @@
     </row>
     <row r="135" spans="1:6">
       <c r="A135" s="1" t="s">
-        <v>403</v>
+        <v>397</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="D135" s="1" t="s">
         <v>58</v>
@@ -8213,7 +8105,7 @@
         <v>64</v>
       </c>
       <c r="F135" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="136" spans="1:6">
@@ -8228,8 +8120,104 @@
         <v>72</v>
       </c>
     </row>
+    <row r="137" spans="1:6">
+      <c r="A137" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="B137" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="C137" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="D137" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E137" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F137" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6">
+      <c r="A138" s="1"/>
+      <c r="B138" s="1"/>
+      <c r="C138" s="1"/>
+      <c r="D138" s="1"/>
+      <c r="E138" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="F138" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6">
+      <c r="A139" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="B139" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="C139" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="D139" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E139" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F139" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6">
+      <c r="A140" s="1"/>
+      <c r="B140" s="1"/>
+      <c r="C140" s="1"/>
+      <c r="D140" s="1"/>
+      <c r="E140" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="F140" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6">
+      <c r="A141" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B141" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="C141" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="D141" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E141" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F141" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6">
+      <c r="A142" s="1"/>
+      <c r="B142" s="1"/>
+      <c r="C142" s="1"/>
+      <c r="D142" s="1"/>
+      <c r="E142" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="F142" t="s">
+        <v>72</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="232">
+  <mergeCells count="244">
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="A5:A6"/>
     <mergeCell ref="A7:A8"/>
@@ -8280,14 +8268,17 @@
     <mergeCell ref="A114:A115"/>
     <mergeCell ref="A116:A117"/>
     <mergeCell ref="A118:A119"/>
-    <mergeCell ref="A121:A122"/>
-    <mergeCell ref="A123:A124"/>
-    <mergeCell ref="A125:A126"/>
+    <mergeCell ref="A120:A121"/>
+    <mergeCell ref="A122:A123"/>
+    <mergeCell ref="A124:A125"/>
     <mergeCell ref="A127:A128"/>
     <mergeCell ref="A129:A130"/>
     <mergeCell ref="A131:A132"/>
     <mergeCell ref="A133:A134"/>
     <mergeCell ref="A135:A136"/>
+    <mergeCell ref="A137:A138"/>
+    <mergeCell ref="A139:A140"/>
+    <mergeCell ref="A141:A142"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="B5:B6"/>
     <mergeCell ref="B7:B8"/>
@@ -8338,14 +8329,17 @@
     <mergeCell ref="B114:B115"/>
     <mergeCell ref="B116:B117"/>
     <mergeCell ref="B118:B119"/>
-    <mergeCell ref="B121:B122"/>
-    <mergeCell ref="B123:B124"/>
-    <mergeCell ref="B125:B126"/>
+    <mergeCell ref="B120:B121"/>
+    <mergeCell ref="B122:B123"/>
+    <mergeCell ref="B124:B125"/>
     <mergeCell ref="B127:B128"/>
     <mergeCell ref="B129:B130"/>
     <mergeCell ref="B131:B132"/>
     <mergeCell ref="B133:B134"/>
     <mergeCell ref="B135:B136"/>
+    <mergeCell ref="B137:B138"/>
+    <mergeCell ref="B139:B140"/>
+    <mergeCell ref="B141:B142"/>
     <mergeCell ref="C3:C4"/>
     <mergeCell ref="C5:C6"/>
     <mergeCell ref="C7:C8"/>
@@ -8396,14 +8390,17 @@
     <mergeCell ref="C114:C115"/>
     <mergeCell ref="C116:C117"/>
     <mergeCell ref="C118:C119"/>
-    <mergeCell ref="C121:C122"/>
-    <mergeCell ref="C123:C124"/>
-    <mergeCell ref="C125:C126"/>
+    <mergeCell ref="C120:C121"/>
+    <mergeCell ref="C122:C123"/>
+    <mergeCell ref="C124:C125"/>
     <mergeCell ref="C127:C128"/>
     <mergeCell ref="C129:C130"/>
     <mergeCell ref="C131:C132"/>
     <mergeCell ref="C133:C134"/>
     <mergeCell ref="C135:C136"/>
+    <mergeCell ref="C137:C138"/>
+    <mergeCell ref="C139:C140"/>
+    <mergeCell ref="C141:C142"/>
     <mergeCell ref="D3:D4"/>
     <mergeCell ref="D5:D6"/>
     <mergeCell ref="D7:D8"/>
@@ -8454,14 +8451,17 @@
     <mergeCell ref="D114:D115"/>
     <mergeCell ref="D116:D117"/>
     <mergeCell ref="D118:D119"/>
-    <mergeCell ref="D121:D122"/>
-    <mergeCell ref="D123:D124"/>
-    <mergeCell ref="D125:D126"/>
+    <mergeCell ref="D120:D121"/>
+    <mergeCell ref="D122:D123"/>
+    <mergeCell ref="D124:D125"/>
     <mergeCell ref="D127:D128"/>
     <mergeCell ref="D129:D130"/>
     <mergeCell ref="D131:D132"/>
     <mergeCell ref="D133:D134"/>
     <mergeCell ref="D135:D136"/>
+    <mergeCell ref="D137:D138"/>
+    <mergeCell ref="D139:D140"/>
+    <mergeCell ref="D141:D142"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
